--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3061165.52</v>
+        <v>3388.55</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4641000</v>
+        <v>5137.35</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>32487000</v>
+        <v>35961.44</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3800860</v>
+        <v>4207.36</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11631577.65</v>
+        <v>12875.56</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>17813490.8</v>
+        <v>19718.62</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2688746.69</v>
+        <v>2976.3</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7522823</v>
+        <v>8327.379999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6194559.28</v>
+        <v>6857.06</v>
       </c>
     </row>
     <row r="11">
@@ -1114,17 +1114,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>57120000</v>
+        <v>63228.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3191-2752-CM26</t>
+          <t>1002772-6905-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,48 +1144,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4422040</v>
+        <v>2939.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1002772-6905-CM26</t>
+          <t>3191-2752-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,42 +1205,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2655437.4</v>
+        <v>4894.97</v>
       </c>
     </row>
     <row r="14">
@@ -1297,17 +1297,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5815530</v>
+        <v>6437.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3471-1979-CM26</t>
+          <t>3328-1342-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1358,17 +1358,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4469473.4</v>
+        <v>4149.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1514-2392-CM26</t>
+          <t>3328-1369-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,43 +1393,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2380000</v>
+        <v>2648.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3328-1342-CM26</t>
+          <t>1514-2392-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,43 +1454,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3748294.13</v>
+        <v>2634.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3328-1369-CM26</t>
+          <t>3471-1979-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>Carabineros de Chile - Hospital de Carabineros</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2392522.37</v>
+        <v>4947.48</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4078575.06</v>
+        <v>4514.77</v>
       </c>
     </row>
     <row r="20">
@@ -1663,17 +1663,17 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4641000</v>
+        <v>5137.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057503-3007-CM26</t>
+          <t>800-3466-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1724,17 +1724,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27520047.1</v>
+        <v>2660.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3328-1444-CM26</t>
+          <t>1057503-3007-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1774,28 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2498660.85</v>
+        <v>30463.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>812030-659-CM26</t>
+          <t>3328-1444-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1835,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3877020</v>
+        <v>2765.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>800-3466-CM26</t>
+          <t>812030-659-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2403800</v>
+        <v>4291.66</v>
       </c>
     </row>
     <row r="25">
@@ -1968,17 +1968,17 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5093200</v>
+        <v>5637.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1952-1225-CM26</t>
+          <t>617807-3451-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,48 +1998,48 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3362314.06</v>
+        <v>7993.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1952-1368-CM26</t>
+          <t>1952-1225-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2090,17 +2090,17 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3264108.12</v>
+        <v>3721.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>617807-3451-CM26</t>
+          <t>1952-1368-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,42 +2120,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7221277</v>
+        <v>3613.2</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3042235</v>
+        <v>3367.6</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2380000</v>
+        <v>2634.54</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2904411.58</v>
+        <v>3215.03</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2284800</v>
+        <v>2529.16</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7176126.02</v>
+        <v>7943.6</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2178414</v>
+        <v>2411.39</v>
       </c>
     </row>
     <row r="35">
@@ -2578,17 +2578,17 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2803759</v>
+        <v>3103.62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3471-2130-CM26</t>
+          <t>1704-3308-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2639,17 +2639,17 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4017532.82</v>
+        <v>2473.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704-3308-CM26</t>
+          <t>3191-3050-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,28 +2689,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2234736.7</v>
+        <v>4894.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3191-3050-CM26</t>
+          <t>1057539-4675-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,48 +2730,48 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4422040</v>
+        <v>5504.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057539-4675-CM26</t>
+          <t>3378-5245-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,48 +2791,48 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4973010</v>
+        <v>3913.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3378-5245-CM26</t>
+          <t>617807-3551-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2857,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3535091.35</v>
+        <v>5548.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>617807-3551-CM26</t>
+          <t>2107-1197-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,48 +2913,48 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5012518</v>
+        <v>30364.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3191-3021-CM26</t>
+          <t>2107-1196-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,17 +2979,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3005,17 +3005,17 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5228860</v>
+        <v>4931.85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2107-1196-CM26</t>
+          <t>2107-1195-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.965.562-K</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4455360</v>
+        <v>2568.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2107-1195-CM26</t>
+          <t>2080-5727-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3116,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2320500</v>
+        <v>29776.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2080-5732-CM26</t>
+          <t>3191-3021-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,48 +3157,48 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5474000</v>
+        <v>5788.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2080-5727-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,53 +3213,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>26899355</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2107-1197-CM26</t>
+          <t>1057539-4657-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3310,17 +3310,17 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>27430452</v>
+        <v>13551.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,28 +3360,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3476072.11</v>
+        <v>4027.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057539-4657-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3401,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12242039.32</v>
+        <v>2520.92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>3328-1493-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,43 +3467,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3638753.44</v>
+        <v>4081.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057539-4560-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,48 +3523,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2277358.93</v>
+        <v>3951.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3328-1493-CM26</t>
+          <t>1057402-6588-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,43 +3589,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3687304.25</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057539-4560-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,48 +3645,48 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3570000</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057402-6588-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3737,17 +3737,17 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3476072.11</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3798,17 +3798,17 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3476072.11</v>
+        <v>4339.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3859,17 +3859,17 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3476072.11</v>
+        <v>4426.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3920,17 +3920,17 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3476072.11</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3981,17 +3981,17 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3998517.81</v>
+        <v>8367.860000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4042,17 +4042,17 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7559390.51</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4103,17 +4103,17 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3476070.92</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4164,17 +4164,17 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3476070.92</v>
+        <v>7088.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4225,17 +4225,17 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6403510.19</v>
+        <v>3847.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4286,17 +4286,17 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3476072.11</v>
+        <v>3962.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4347,17 +4347,17 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3579779.42</v>
+        <v>4339.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1549-2697-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,43 +4382,43 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3920531.16</v>
+        <v>68958.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1549-2703-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,43 +4443,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3920531.16</v>
+        <v>15065.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1549-2697-CM26</t>
+          <t>1549-2705-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4530,17 +4530,17 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>62295905</v>
+        <v>56234.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1549-2703-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4591,17 +4591,17 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13609554</v>
+        <v>14643.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1549-2705-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4652,17 +4652,17 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>50801457</v>
+        <v>28242.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>3191-3137-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,43 +4687,43 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>13228278</v>
+        <v>3235.21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4774,17 +4774,17 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>25513600</v>
+        <v>6291.28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2111-10014-CM26</t>
+          <t>2111-10040-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4824,28 +4824,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>IMPORTADORA MOTAC SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.594.461-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2677500</v>
+        <v>4185.38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1380-8108-CM26</t>
+          <t>3191-3135-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,48 +4865,48 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2185792</v>
+        <v>5216.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>1380-8108-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,48 +4926,48 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5683440</v>
+        <v>2419.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3191-3137-CM26</t>
+          <t>608-7488-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4987,17 +4987,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,28 +5007,28 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2922640</v>
+        <v>2530.34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2111-10040-CM26</t>
+          <t>2111-9985-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5079,17 +5079,17 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3781008.42</v>
+        <v>16741.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057539-4797-CM26</t>
+          <t>3328-1542-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5114,43 +5114,43 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>56261400.72</v>
+        <v>4550.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>608-7488-CM26</t>
+          <t>1057539-4797-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,43 +5175,43 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2285871</v>
+        <v>62278.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2111-9985-CM26</t>
+          <t>5326-859-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,43 +5236,43 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>15124033.68</v>
+        <v>15191.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3328-1542-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,53 +5287,53 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4110919.26</v>
+        <v>2444.98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3191-3135-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,28 +5373,28 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4712400</v>
+        <v>4324.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5326-859-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5419,43 +5419,43 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>13724032</v>
+        <v>2444.98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,28 +5495,28 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2208759</v>
+        <v>5554.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>3328-1516-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5536,48 +5536,48 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3906948.5</v>
+        <v>3806.96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>1952-1616-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5628,17 +5628,17 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2208759</v>
+        <v>2395.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>812030-613-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,48 +5658,48 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5018157.41</v>
+        <v>74521.42999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3328-1516-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,43 +5724,43 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3439144.03</v>
+        <v>7904.67</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1952-1616-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,43 +5785,43 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2164144.71</v>
+        <v>19248.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>812030-613-CM26</t>
+          <t>1057539-4868-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,53 +5836,53 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>67321489.2</v>
+        <v>21932.53</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>2258-5366-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,43 +5907,43 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7140952</v>
+        <v>17775.25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5983,28 +5983,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17388399</v>
+        <v>22218.85</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057539-4868-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,43 +6029,43 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>19813500</v>
+        <v>4378.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2258-5366-CM26</t>
+          <t>1952-1685-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,53 +6080,53 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>16057877.85</v>
+        <v>76659.10000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,27 +6141,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6177,17 +6177,17 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>20072158.4</v>
+        <v>46288.97</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>1057539-4947-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,48 +6207,48 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4746805.28</v>
+        <v>55325.29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6299,17 +6299,17 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>27643700</v>
+        <v>47454.61</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>5326-865-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6360,17 +6360,17 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>42869750</v>
+        <v>30600.16</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057539-4947-CM26</t>
+          <t>1057489-8114-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,48 +6390,48 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>49980000</v>
+        <v>5254.47</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1952-1685-CM26</t>
+          <t>2111-10165-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,342 +6456,37 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>69252630.72</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2111-10065-CM26</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Enviada a Proveedor</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>61.608.602-2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>TECNOMEDICAL S A</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>3034500</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>3191-3081-CM26</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Enviada a Proveedor</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>61.102.017-1</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>BIOMET CHILE S A</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>17430301.28</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2111-10164-CM26</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>61.608.602-2</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>3955356.51</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>812030-712-CM26</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>65.075.485-9</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>41816730.9</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2111-10165-CM26</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>61.608.602-2</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>BIOMET CHILE S A</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>4110919.26</v>
+        <v>4550.58</v>
       </c>
     </row>
   </sheetData>
